--- a/tests/report/test-analysis.xlsx
+++ b/tests/report/test-analysis.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="399">
   <si>
     <t>Item</t>
   </si>
@@ -165,7 +165,7 @@
     <t>Search found</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:26.866Z</t>
+    <t>2026-06-13T09:03:53.306Z</t>
   </si>
   <si>
     <t>Interactive elements are keyboard focusable</t>
@@ -180,9 +180,6 @@
     <t>Keyboard support</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:26.867Z</t>
-  </si>
-  <si>
     <t>Images and icons have alt text or aria labels</t>
   </si>
   <si>
@@ -216,7 +213,7 @@
     <t>Vite build configured</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:16.064Z</t>
+    <t>2026-06-13T09:03:41.588Z</t>
   </si>
   <si>
     <t>Production preview serves correctly</t>
@@ -228,7 +225,7 @@
     <t>Vite preview available</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:16.065Z</t>
+    <t>2026-06-13T09:03:41.601Z</t>
   </si>
   <si>
     <t>Network requests use HTTPS for backend</t>
@@ -249,7 +246,7 @@
     <t>Home page rendered</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.067Z</t>
+    <t>2026-06-13T09:03:44.637Z</t>
   </si>
   <si>
     <t>Application is route-guarded by client side routing</t>
@@ -294,7 +291,7 @@
     <t>Page refresh succeeds</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:25.865Z</t>
+    <t>2026-06-13T09:03:52.303Z</t>
   </si>
   <si>
     <t>App is installable as PWA placeholder</t>
@@ -312,7 +309,7 @@
     <t>Home loads</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.275Z</t>
+    <t>2026-06-13T09:03:44.968Z</t>
   </si>
   <si>
     <t>Dashboard route loads</t>
@@ -333,7 +330,7 @@
     <t>Jobs page loaded</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.483Z</t>
+    <t>2026-06-13T09:03:45.441Z</t>
   </si>
   <si>
     <t>Analytics route loads</t>
@@ -345,7 +342,7 @@
     <t>Analytics loaded</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:22.202Z</t>
+    <t>2026-06-13T09:03:48.849Z</t>
   </si>
   <si>
     <t>Search filters job cards</t>
@@ -357,7 +354,7 @@
     <t>Query entered</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:20.899Z</t>
+    <t>2026-06-13T09:03:47.306Z</t>
   </si>
   <si>
     <t>Location filter works</t>
@@ -399,7 +396,7 @@
     <t>100 jobs returned</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:25.300Z</t>
+    <t>2026-06-13T09:03:51.695Z</t>
   </si>
   <si>
     <t>Error state displays on API failure</t>
@@ -459,7 +456,7 @@
     <t>Resized back to desktop</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:24.717Z</t>
+    <t>2026-06-13T09:03:51.316Z</t>
   </si>
   <si>
     <t>Analytics page handles no-data gracefully</t>
@@ -501,7 +498,7 @@
     <t>0 items</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:22.129Z</t>
+    <t>2026-06-13T09:03:48.748Z</t>
   </si>
   <si>
     <t>Hover effects do not break layout</t>
@@ -555,7 +552,7 @@
     <t>Found 1 headings</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.080Z</t>
+    <t>2026-06-13T09:03:44.662Z</t>
   </si>
   <si>
     <t>Navigation bar renders on desktop</t>
@@ -567,7 +564,7 @@
     <t>Found 3 nav items</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.345Z</t>
+    <t>2026-06-13T09:03:45.255Z</t>
   </si>
   <si>
     <t>Sidebar toggles correctly</t>
@@ -579,7 +576,7 @@
     <t>Found 10 features</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.092Z</t>
+    <t>2026-06-13T09:03:44.682Z</t>
   </si>
   <si>
     <t>Page headings are readable</t>
@@ -600,7 +597,7 @@
     <t>Search field found</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.869Z</t>
+    <t>2026-06-13T09:03:45.535Z</t>
   </si>
   <si>
     <t>Filter controls are aligned</t>
@@ -612,7 +609,7 @@
     <t>Found 2 filters</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.880Z</t>
+    <t>2026-06-13T09:03:45.576Z</t>
   </si>
   <si>
     <t>Job cards render in a responsive grid</t>
@@ -621,10 +618,10 @@
     <t>Grid layout adapts without overlap.</t>
   </si>
   <si>
-    <t>Found 6 jobs</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:20.915Z</t>
+    <t>Found 5 jobs</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:03:47.341Z</t>
   </si>
   <si>
     <t>Apply button is accessible on job cards</t>
@@ -633,10 +630,10 @@
     <t>Apply button appears on each job card.</t>
   </si>
   <si>
-    <t>Found 6 buttons</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:20.925Z</t>
+    <t>Found 5 buttons</t>
+  </si>
+  <si>
+    <t>2026-06-13T09:03:47.359Z</t>
   </si>
   <si>
     <t>Dashboard summary cards are visible</t>
@@ -648,7 +645,7 @@
     <t>Found 16 cards</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.372Z</t>
+    <t>2026-06-13T09:03:45.271Z</t>
   </si>
   <si>
     <t>Analytics charts render after data load</t>
@@ -696,7 +693,7 @@
     <t>Resized to mobile</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:23.774Z</t>
+    <t>2026-06-13T09:03:50.463Z</t>
   </si>
   <si>
     <t>Live status badge is visible on dashboard</t>
@@ -849,7 +846,7 @@
     <t>Search cleared</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:20.946Z</t>
+    <t>2026-06-13T09:03:47.401Z</t>
   </si>
   <si>
     <t>Location filter handles invalid selection</t>
@@ -1050,7 +1047,7 @@
     <t>Found 2 buttons</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.102Z</t>
+    <t>2026-06-13T09:03:44.701Z</t>
   </si>
   <si>
     <t>Hero CTAs</t>
@@ -1059,7 +1056,7 @@
     <t>Found 2 hero actions</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.116Z</t>
+    <t>2026-06-13T09:03:44.719Z</t>
   </si>
   <si>
     <t>Functional</t>
@@ -1945,7 +1942,7 @@
         <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1953,16 +1950,16 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
         <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
       </c>
       <c r="D4" t="s">
         <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -1976,10 +1973,10 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
         <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>58</v>
       </c>
       <c r="D5" t="s">
         <v>45</v>
@@ -1988,10 +1985,10 @@
         <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1999,16 +1996,16 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
         <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
       </c>
       <c r="D6" t="s">
         <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" t="s">
         <v>9</v>
@@ -2064,10 +2061,10 @@
         <v>91</v>
       </c>
       <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
         <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>63</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
@@ -2076,10 +2073,10 @@
         <v>46</v>
       </c>
       <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
         <v>64</v>
-      </c>
-      <c r="G2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2087,10 +2084,10 @@
         <v>92</v>
       </c>
       <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
         <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
       </c>
       <c r="D3" t="s">
         <v>45</v>
@@ -2099,10 +2096,10 @@
         <v>46</v>
       </c>
       <c r="F3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" t="s">
         <v>68</v>
-      </c>
-      <c r="G3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2110,10 +2107,10 @@
         <v>93</v>
       </c>
       <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" t="s">
         <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -2122,10 +2119,10 @@
         <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2133,10 +2130,10 @@
         <v>94</v>
       </c>
       <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" t="s">
         <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -2145,10 +2142,10 @@
         <v>46</v>
       </c>
       <c r="F5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" t="s">
         <v>75</v>
-      </c>
-      <c r="G5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2156,10 +2153,10 @@
         <v>95</v>
       </c>
       <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
         <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>45</v>
@@ -2168,7 +2165,7 @@
         <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s">
         <v>48</v>
@@ -2179,16 +2176,16 @@
         <v>96</v>
       </c>
       <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
         <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -2202,16 +2199,16 @@
         <v>97</v>
       </c>
       <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
         <v>82</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>83</v>
       </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -2225,10 +2222,10 @@
         <v>98</v>
       </c>
       <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
       </c>
       <c r="D9" t="s">
         <v>51</v>
@@ -2237,7 +2234,7 @@
         <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s">
         <v>48</v>
@@ -2248,10 +2245,10 @@
         <v>99</v>
       </c>
       <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
         <v>88</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -2260,10 +2257,10 @@
         <v>46</v>
       </c>
       <c r="F10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" t="s">
         <v>90</v>
-      </c>
-      <c r="G10" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2271,16 +2268,16 @@
         <v>100</v>
       </c>
       <c r="B11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" t="s">
         <v>92</v>
       </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
@@ -2336,10 +2333,10 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
@@ -2348,10 +2345,10 @@
         <v>46</v>
       </c>
       <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" t="s">
         <v>96</v>
-      </c>
-      <c r="G2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2359,10 +2356,10 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s">
         <v>98</v>
-      </c>
-      <c r="C3" t="s">
-        <v>99</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
@@ -2371,10 +2368,10 @@
         <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2382,10 +2379,10 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
         <v>101</v>
-      </c>
-      <c r="C4" t="s">
-        <v>102</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -2394,10 +2391,10 @@
         <v>46</v>
       </c>
       <c r="F4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" t="s">
         <v>103</v>
-      </c>
-      <c r="G4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2405,10 +2402,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
         <v>105</v>
-      </c>
-      <c r="C5" t="s">
-        <v>106</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -2417,10 +2414,10 @@
         <v>46</v>
       </c>
       <c r="F5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" t="s">
         <v>107</v>
-      </c>
-      <c r="G5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2428,10 +2425,10 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="s">
         <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>110</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -2440,10 +2437,10 @@
         <v>46</v>
       </c>
       <c r="F6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" t="s">
         <v>111</v>
-      </c>
-      <c r="G6" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2451,10 +2448,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" t="s">
         <v>113</v>
-      </c>
-      <c r="C7" t="s">
-        <v>114</v>
       </c>
       <c r="D7" t="s">
         <v>51</v>
@@ -2463,10 +2460,10 @@
         <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2474,10 +2471,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
         <v>116</v>
-      </c>
-      <c r="C8" t="s">
-        <v>117</v>
       </c>
       <c r="D8" t="s">
         <v>51</v>
@@ -2486,10 +2483,10 @@
         <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2497,10 +2494,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" t="s">
         <v>118</v>
-      </c>
-      <c r="C9" t="s">
-        <v>119</v>
       </c>
       <c r="D9" t="s">
         <v>51</v>
@@ -2509,10 +2506,10 @@
         <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2520,16 +2517,16 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
         <v>121</v>
-      </c>
-      <c r="C10" t="s">
-        <v>122</v>
       </c>
       <c r="D10" t="s">
         <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -2543,10 +2540,10 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" t="s">
         <v>123</v>
-      </c>
-      <c r="C11" t="s">
-        <v>124</v>
       </c>
       <c r="D11" t="s">
         <v>51</v>
@@ -2555,10 +2552,10 @@
         <v>46</v>
       </c>
       <c r="F11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" t="s">
         <v>125</v>
-      </c>
-      <c r="G11" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2566,16 +2563,16 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
         <v>127</v>
-      </c>
-      <c r="C12" t="s">
-        <v>128</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
@@ -2589,16 +2586,16 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" t="s">
         <v>129</v>
-      </c>
-      <c r="C13" t="s">
-        <v>130</v>
       </c>
       <c r="D13" t="s">
         <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -2612,16 +2609,16 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" t="s">
         <v>131</v>
-      </c>
-      <c r="C14" t="s">
-        <v>132</v>
       </c>
       <c r="D14" t="s">
         <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -2635,16 +2632,16 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" t="s">
         <v>133</v>
-      </c>
-      <c r="C15" t="s">
-        <v>134</v>
       </c>
       <c r="D15" t="s">
         <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -2658,16 +2655,16 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" t="s">
         <v>135</v>
-      </c>
-      <c r="C16" t="s">
-        <v>136</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
@@ -2681,10 +2678,10 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" t="s">
         <v>137</v>
-      </c>
-      <c r="C17" t="s">
-        <v>138</v>
       </c>
       <c r="D17" t="s">
         <v>51</v>
@@ -2693,10 +2690,10 @@
         <v>46</v>
       </c>
       <c r="F17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2704,10 +2701,10 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" t="s">
         <v>140</v>
-      </c>
-      <c r="C18" t="s">
-        <v>141</v>
       </c>
       <c r="D18" t="s">
         <v>51</v>
@@ -2716,10 +2713,10 @@
         <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2727,10 +2724,10 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" t="s">
         <v>143</v>
-      </c>
-      <c r="C19" t="s">
-        <v>144</v>
       </c>
       <c r="D19" t="s">
         <v>45</v>
@@ -2739,10 +2736,10 @@
         <v>46</v>
       </c>
       <c r="F19" t="s">
+        <v>144</v>
+      </c>
+      <c r="G19" t="s">
         <v>145</v>
-      </c>
-      <c r="G19" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2750,16 +2747,16 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" t="s">
         <v>147</v>
-      </c>
-      <c r="C20" t="s">
-        <v>148</v>
       </c>
       <c r="D20" t="s">
         <v>45</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -2773,16 +2770,16 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" t="s">
         <v>149</v>
-      </c>
-      <c r="C21" t="s">
-        <v>150</v>
       </c>
       <c r="D21" t="s">
         <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -2796,16 +2793,16 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" t="s">
         <v>151</v>
-      </c>
-      <c r="C22" t="s">
-        <v>152</v>
       </c>
       <c r="D22" t="s">
         <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
         <v>9</v>
@@ -2819,16 +2816,16 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" t="s">
         <v>153</v>
-      </c>
-      <c r="C23" t="s">
-        <v>154</v>
       </c>
       <c r="D23" t="s">
         <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
@@ -2842,16 +2839,16 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" t="s">
         <v>155</v>
-      </c>
-      <c r="C24" t="s">
-        <v>156</v>
       </c>
       <c r="D24" t="s">
         <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -2865,10 +2862,10 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" t="s">
         <v>157</v>
-      </c>
-      <c r="C25" t="s">
-        <v>158</v>
       </c>
       <c r="D25" t="s">
         <v>51</v>
@@ -2877,10 +2874,10 @@
         <v>46</v>
       </c>
       <c r="F25" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" t="s">
         <v>159</v>
-      </c>
-      <c r="G25" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2888,22 +2885,22 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" t="s">
         <v>161</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" t="s">
         <v>162</v>
       </c>
-      <c r="D26" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" t="s">
-        <v>46</v>
-      </c>
-      <c r="F26" t="s">
-        <v>163</v>
-      </c>
       <c r="G26" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2911,16 +2908,16 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" t="s">
         <v>164</v>
-      </c>
-      <c r="C27" t="s">
-        <v>165</v>
       </c>
       <c r="D27" t="s">
         <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
@@ -2934,16 +2931,16 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" t="s">
         <v>166</v>
-      </c>
-      <c r="C28" t="s">
-        <v>167</v>
       </c>
       <c r="D28" t="s">
         <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
         <v>9</v>
@@ -2957,16 +2954,16 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" t="s">
         <v>168</v>
-      </c>
-      <c r="C29" t="s">
-        <v>169</v>
       </c>
       <c r="D29" t="s">
         <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
         <v>9</v>
@@ -2980,10 +2977,10 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" t="s">
         <v>170</v>
-      </c>
-      <c r="C30" t="s">
-        <v>171</v>
       </c>
       <c r="D30" t="s">
         <v>45</v>
@@ -2992,10 +2989,10 @@
         <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G30" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -3003,16 +3000,16 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" t="s">
         <v>173</v>
-      </c>
-      <c r="C31" t="s">
-        <v>174</v>
       </c>
       <c r="D31" t="s">
         <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
         <v>9</v>
@@ -3068,10 +3065,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" t="s">
         <v>175</v>
-      </c>
-      <c r="C2" t="s">
-        <v>176</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
@@ -3080,10 +3077,10 @@
         <v>46</v>
       </c>
       <c r="F2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" t="s">
         <v>177</v>
-      </c>
-      <c r="G2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3091,10 +3088,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" t="s">
         <v>179</v>
-      </c>
-      <c r="C3" t="s">
-        <v>180</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
@@ -3103,10 +3100,10 @@
         <v>46</v>
       </c>
       <c r="F3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" t="s">
         <v>181</v>
-      </c>
-      <c r="G3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3114,10 +3111,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" t="s">
         <v>183</v>
-      </c>
-      <c r="C4" t="s">
-        <v>184</v>
       </c>
       <c r="D4" t="s">
         <v>45</v>
@@ -3126,10 +3123,10 @@
         <v>46</v>
       </c>
       <c r="F4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" t="s">
         <v>185</v>
-      </c>
-      <c r="G4" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3137,10 +3134,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" t="s">
         <v>187</v>
-      </c>
-      <c r="C5" t="s">
-        <v>188</v>
       </c>
       <c r="D5" t="s">
         <v>45</v>
@@ -3149,10 +3146,10 @@
         <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -3160,10 +3157,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" t="s">
         <v>190</v>
-      </c>
-      <c r="C6" t="s">
-        <v>191</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -3172,10 +3169,10 @@
         <v>46</v>
       </c>
       <c r="F6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G6" t="s">
         <v>192</v>
-      </c>
-      <c r="G6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3183,10 +3180,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" t="s">
         <v>194</v>
-      </c>
-      <c r="C7" t="s">
-        <v>195</v>
       </c>
       <c r="D7" t="s">
         <v>45</v>
@@ -3195,10 +3192,10 @@
         <v>46</v>
       </c>
       <c r="F7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G7" t="s">
         <v>196</v>
-      </c>
-      <c r="G7" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3206,10 +3203,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" t="s">
         <v>198</v>
-      </c>
-      <c r="C8" t="s">
-        <v>199</v>
       </c>
       <c r="D8" t="s">
         <v>51</v>
@@ -3218,10 +3215,10 @@
         <v>46</v>
       </c>
       <c r="F8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G8" t="s">
         <v>200</v>
-      </c>
-      <c r="G8" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -3229,10 +3226,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" t="s">
         <v>202</v>
-      </c>
-      <c r="C9" t="s">
-        <v>203</v>
       </c>
       <c r="D9" t="s">
         <v>51</v>
@@ -3241,10 +3238,10 @@
         <v>46</v>
       </c>
       <c r="F9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" t="s">
         <v>204</v>
-      </c>
-      <c r="G9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -3252,10 +3249,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" t="s">
         <v>206</v>
-      </c>
-      <c r="C10" t="s">
-        <v>207</v>
       </c>
       <c r="D10" t="s">
         <v>45</v>
@@ -3264,10 +3261,10 @@
         <v>46</v>
       </c>
       <c r="F10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G10" t="s">
         <v>208</v>
-      </c>
-      <c r="G10" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -3275,10 +3272,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" t="s">
         <v>210</v>
-      </c>
-      <c r="C11" t="s">
-        <v>211</v>
       </c>
       <c r="D11" t="s">
         <v>51</v>
@@ -3287,10 +3284,10 @@
         <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3298,22 +3295,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" t="s">
         <v>213</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" t="s">
         <v>214</v>
       </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s">
-        <v>215</v>
-      </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3321,22 +3318,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" t="s">
         <v>216</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" t="s">
         <v>217</v>
       </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" t="s">
-        <v>218</v>
-      </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3344,10 +3341,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>218</v>
+      </c>
+      <c r="C14" t="s">
         <v>219</v>
-      </c>
-      <c r="C14" t="s">
-        <v>220</v>
       </c>
       <c r="D14" t="s">
         <v>45</v>
@@ -3356,10 +3353,10 @@
         <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3367,10 +3364,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15" t="s">
         <v>222</v>
-      </c>
-      <c r="C15" t="s">
-        <v>223</v>
       </c>
       <c r="D15" t="s">
         <v>51</v>
@@ -3379,10 +3376,10 @@
         <v>46</v>
       </c>
       <c r="F15" t="s">
+        <v>223</v>
+      </c>
+      <c r="G15" t="s">
         <v>224</v>
-      </c>
-      <c r="G15" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3390,10 +3387,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" t="s">
         <v>226</v>
-      </c>
-      <c r="C16" t="s">
-        <v>227</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
@@ -3402,10 +3399,10 @@
         <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3455,10 +3452,10 @@
         <v>71</v>
       </c>
       <c r="B2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" t="s">
         <v>229</v>
-      </c>
-      <c r="C2" t="s">
-        <v>230</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
@@ -3467,10 +3464,10 @@
         <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3478,16 +3475,16 @@
         <v>72</v>
       </c>
       <c r="B3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" t="s">
         <v>232</v>
-      </c>
-      <c r="C3" t="s">
-        <v>233</v>
       </c>
       <c r="D3" t="s">
         <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -3501,10 +3498,10 @@
         <v>73</v>
       </c>
       <c r="B4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" t="s">
         <v>234</v>
-      </c>
-      <c r="C4" t="s">
-        <v>235</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -3513,10 +3510,10 @@
         <v>46</v>
       </c>
       <c r="F4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3524,16 +3521,16 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" t="s">
         <v>237</v>
-      </c>
-      <c r="C5" t="s">
-        <v>238</v>
       </c>
       <c r="D5" t="s">
         <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -3547,10 +3544,10 @@
         <v>75</v>
       </c>
       <c r="B6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" t="s">
         <v>239</v>
-      </c>
-      <c r="C6" t="s">
-        <v>240</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -3559,10 +3556,10 @@
         <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -3570,10 +3567,10 @@
         <v>76</v>
       </c>
       <c r="B7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" t="s">
         <v>242</v>
-      </c>
-      <c r="C7" t="s">
-        <v>243</v>
       </c>
       <c r="D7" t="s">
         <v>51</v>
@@ -3582,10 +3579,10 @@
         <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -3593,16 +3590,16 @@
         <v>77</v>
       </c>
       <c r="B8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" t="s">
         <v>245</v>
       </c>
-      <c r="C8" t="s">
-        <v>246</v>
-      </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -3616,16 +3613,16 @@
         <v>78</v>
       </c>
       <c r="B9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" t="s">
         <v>247</v>
       </c>
-      <c r="C9" t="s">
-        <v>248</v>
-      </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -3639,16 +3636,16 @@
         <v>79</v>
       </c>
       <c r="B10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" t="s">
         <v>249</v>
-      </c>
-      <c r="C10" t="s">
-        <v>250</v>
       </c>
       <c r="D10" t="s">
         <v>45</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" t="s">
         <v>9</v>
@@ -3662,16 +3659,16 @@
         <v>80</v>
       </c>
       <c r="B11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" t="s">
         <v>251</v>
-      </c>
-      <c r="C11" t="s">
-        <v>252</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
         <v>9</v>
@@ -3685,16 +3682,16 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" t="s">
         <v>253</v>
-      </c>
-      <c r="C12" t="s">
-        <v>254</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
@@ -3708,16 +3705,16 @@
         <v>82</v>
       </c>
       <c r="B13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" t="s">
         <v>255</v>
-      </c>
-      <c r="C13" t="s">
-        <v>256</v>
       </c>
       <c r="D13" t="s">
         <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -3731,16 +3728,16 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" t="s">
         <v>257</v>
       </c>
-      <c r="C14" t="s">
-        <v>258</v>
-      </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -3754,16 +3751,16 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" t="s">
         <v>259</v>
-      </c>
-      <c r="C15" t="s">
-        <v>260</v>
       </c>
       <c r="D15" t="s">
         <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -3777,16 +3774,16 @@
         <v>85</v>
       </c>
       <c r="B16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" t="s">
         <v>261</v>
-      </c>
-      <c r="C16" t="s">
-        <v>262</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
@@ -3800,16 +3797,16 @@
         <v>86</v>
       </c>
       <c r="B17" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" t="s">
         <v>263</v>
-      </c>
-      <c r="C17" t="s">
-        <v>264</v>
       </c>
       <c r="D17" t="s">
         <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -3823,16 +3820,16 @@
         <v>87</v>
       </c>
       <c r="B18" t="s">
+        <v>264</v>
+      </c>
+      <c r="C18" t="s">
         <v>265</v>
-      </c>
-      <c r="C18" t="s">
-        <v>266</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
@@ -3846,16 +3843,16 @@
         <v>88</v>
       </c>
       <c r="B19" t="s">
+        <v>266</v>
+      </c>
+      <c r="C19" t="s">
         <v>267</v>
       </c>
-      <c r="C19" t="s">
-        <v>268</v>
-      </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -3869,16 +3866,16 @@
         <v>89</v>
       </c>
       <c r="B20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C20" t="s">
         <v>269</v>
       </c>
-      <c r="C20" t="s">
-        <v>270</v>
-      </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -3892,16 +3889,16 @@
         <v>90</v>
       </c>
       <c r="B21" t="s">
+        <v>270</v>
+      </c>
+      <c r="C21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" t="s">
-        <v>272</v>
-      </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -3957,10 +3954,10 @@
         <v>46</v>
       </c>
       <c r="B2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" t="s">
         <v>273</v>
-      </c>
-      <c r="C2" t="s">
-        <v>274</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
@@ -3969,10 +3966,10 @@
         <v>46</v>
       </c>
       <c r="F2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2" t="s">
         <v>275</v>
-      </c>
-      <c r="G2" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -3980,16 +3977,16 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" t="s">
         <v>277</v>
-      </c>
-      <c r="C3" t="s">
-        <v>278</v>
       </c>
       <c r="D3" t="s">
         <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -4003,16 +4000,16 @@
         <v>48</v>
       </c>
       <c r="B4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" t="s">
         <v>279</v>
-      </c>
-      <c r="C4" t="s">
-        <v>280</v>
       </c>
       <c r="D4" t="s">
         <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
@@ -4026,16 +4023,16 @@
         <v>49</v>
       </c>
       <c r="B5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" t="s">
         <v>281</v>
-      </c>
-      <c r="C5" t="s">
-        <v>282</v>
       </c>
       <c r="D5" t="s">
         <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -4049,10 +4046,10 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" t="s">
         <v>283</v>
-      </c>
-      <c r="C6" t="s">
-        <v>284</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
@@ -4061,10 +4058,10 @@
         <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4072,16 +4069,16 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C7" t="s">
         <v>286</v>
-      </c>
-      <c r="C7" t="s">
-        <v>287</v>
       </c>
       <c r="D7" t="s">
         <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
@@ -4095,16 +4092,16 @@
         <v>52</v>
       </c>
       <c r="B8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C8" t="s">
         <v>288</v>
-      </c>
-      <c r="C8" t="s">
-        <v>289</v>
       </c>
       <c r="D8" t="s">
         <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
         <v>9</v>
@@ -4118,16 +4115,16 @@
         <v>53</v>
       </c>
       <c r="B9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" t="s">
         <v>290</v>
-      </c>
-      <c r="C9" t="s">
-        <v>291</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
         <v>9</v>
@@ -4141,10 +4138,10 @@
         <v>54</v>
       </c>
       <c r="B10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" t="s">
         <v>292</v>
-      </c>
-      <c r="C10" t="s">
-        <v>293</v>
       </c>
       <c r="D10" t="s">
         <v>45</v>
@@ -4153,10 +4150,10 @@
         <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4164,10 +4161,10 @@
         <v>55</v>
       </c>
       <c r="B11" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" t="s">
         <v>295</v>
-      </c>
-      <c r="C11" t="s">
-        <v>296</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -4176,10 +4173,10 @@
         <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4187,16 +4184,16 @@
         <v>56</v>
       </c>
       <c r="B12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" t="s">
         <v>298</v>
-      </c>
-      <c r="C12" t="s">
-        <v>299</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>9</v>
@@ -4210,16 +4207,16 @@
         <v>57</v>
       </c>
       <c r="B13" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" t="s">
         <v>300</v>
-      </c>
-      <c r="C13" t="s">
-        <v>301</v>
       </c>
       <c r="D13" t="s">
         <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
         <v>9</v>
@@ -4233,16 +4230,16 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s">
         <v>9</v>
@@ -4256,16 +4253,16 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
+        <v>302</v>
+      </c>
+      <c r="C15" t="s">
         <v>303</v>
-      </c>
-      <c r="C15" t="s">
-        <v>304</v>
       </c>
       <c r="D15" t="s">
         <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
         <v>9</v>
@@ -4279,16 +4276,16 @@
         <v>60</v>
       </c>
       <c r="B16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C16" t="s">
         <v>305</v>
-      </c>
-      <c r="C16" t="s">
-        <v>306</v>
       </c>
       <c r="D16" t="s">
         <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
         <v>9</v>
@@ -4302,16 +4299,16 @@
         <v>61</v>
       </c>
       <c r="B17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C17" t="s">
         <v>307</v>
       </c>
-      <c r="C17" t="s">
-        <v>308</v>
-      </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
@@ -4325,10 +4322,10 @@
         <v>62</v>
       </c>
       <c r="B18" t="s">
+        <v>308</v>
+      </c>
+      <c r="C18" t="s">
         <v>309</v>
-      </c>
-      <c r="C18" t="s">
-        <v>310</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
@@ -4337,10 +4334,10 @@
         <v>46</v>
       </c>
       <c r="F18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -4348,16 +4345,16 @@
         <v>63</v>
       </c>
       <c r="B19" t="s">
+        <v>311</v>
+      </c>
+      <c r="C19" t="s">
         <v>312</v>
       </c>
-      <c r="C19" t="s">
-        <v>313</v>
-      </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
         <v>9</v>
@@ -4371,16 +4368,16 @@
         <v>64</v>
       </c>
       <c r="B20" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" t="s">
         <v>314</v>
       </c>
-      <c r="C20" t="s">
-        <v>315</v>
-      </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
         <v>9</v>
@@ -4394,16 +4391,16 @@
         <v>65</v>
       </c>
       <c r="B21" t="s">
+        <v>315</v>
+      </c>
+      <c r="C21" t="s">
         <v>316</v>
-      </c>
-      <c r="C21" t="s">
-        <v>317</v>
       </c>
       <c r="D21" t="s">
         <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
@@ -4417,10 +4414,10 @@
         <v>66</v>
       </c>
       <c r="B22" t="s">
+        <v>317</v>
+      </c>
+      <c r="C22" t="s">
         <v>318</v>
-      </c>
-      <c r="C22" t="s">
-        <v>319</v>
       </c>
       <c r="D22" t="s">
         <v>51</v>
@@ -4429,10 +4426,10 @@
         <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G22" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -4440,10 +4437,10 @@
         <v>67</v>
       </c>
       <c r="B23" t="s">
+        <v>320</v>
+      </c>
+      <c r="C23" t="s">
         <v>321</v>
-      </c>
-      <c r="C23" t="s">
-        <v>322</v>
       </c>
       <c r="D23" t="s">
         <v>45</v>
@@ -4452,10 +4449,10 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G23" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -4463,16 +4460,16 @@
         <v>68</v>
       </c>
       <c r="B24" t="s">
+        <v>323</v>
+      </c>
+      <c r="C24" t="s">
         <v>324</v>
       </c>
-      <c r="C24" t="s">
-        <v>325</v>
-      </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F24" t="s">
         <v>9</v>
@@ -4486,10 +4483,10 @@
         <v>69</v>
       </c>
       <c r="B25" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" t="s">
         <v>326</v>
-      </c>
-      <c r="C25" t="s">
-        <v>327</v>
       </c>
       <c r="D25" t="s">
         <v>45</v>
@@ -4498,10 +4495,10 @@
         <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -4509,16 +4506,16 @@
         <v>70</v>
       </c>
       <c r="B26" t="s">
+        <v>328</v>
+      </c>
+      <c r="C26" t="s">
         <v>329</v>
       </c>
-      <c r="C26" t="s">
-        <v>330</v>
-      </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s">
         <v>9</v>
@@ -4540,10 +4537,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B1" t="s">
         <v>331</v>
-      </c>
-      <c r="B1" t="s">
-        <v>332</v>
       </c>
       <c r="C1" t="s">
         <v>37</v>
@@ -4563,19 +4560,19 @@
         <v>91</v>
       </c>
       <c r="B2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" t="s">
         <v>333</v>
       </c>
-      <c r="C2" t="s">
-        <v>334</v>
-      </c>
       <c r="D2" t="s">
         <v>46</v>
       </c>
       <c r="E2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" t="s">
         <v>64</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4583,19 +4580,19 @@
         <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D3" t="s">
         <v>46</v>
       </c>
       <c r="E3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" t="s">
         <v>68</v>
-      </c>
-      <c r="F3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -4603,19 +4600,19 @@
         <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D4" t="s">
         <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4623,19 +4620,19 @@
         <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D5" t="s">
         <v>46</v>
       </c>
       <c r="E5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" t="s">
         <v>75</v>
-      </c>
-      <c r="F5" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4643,19 +4640,19 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" t="s">
         <v>338</v>
       </c>
-      <c r="C6" t="s">
-        <v>339</v>
-      </c>
       <c r="D6" t="s">
         <v>46</v>
       </c>
       <c r="E6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" t="s">
         <v>177</v>
-      </c>
-      <c r="F6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4663,19 +4660,19 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D7" t="s">
         <v>46</v>
       </c>
       <c r="E7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" t="s">
         <v>185</v>
-      </c>
-      <c r="F7" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4683,19 +4680,19 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
         <v>341</v>
       </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>342</v>
-      </c>
-      <c r="F8" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4703,19 +4700,19 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C9" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
         <v>344</v>
       </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>345</v>
-      </c>
-      <c r="F9" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4723,19 +4720,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" t="s">
         <v>347</v>
       </c>
-      <c r="C10" t="s">
-        <v>348</v>
-      </c>
       <c r="D10" t="s">
         <v>46</v>
       </c>
       <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
         <v>96</v>
-      </c>
-      <c r="F10" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4743,19 +4740,19 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D11" t="s">
         <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4763,19 +4760,19 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D12" t="s">
         <v>46</v>
       </c>
       <c r="E12" t="s">
+        <v>180</v>
+      </c>
+      <c r="F12" t="s">
         <v>181</v>
-      </c>
-      <c r="F12" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4783,19 +4780,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D13" t="s">
         <v>46</v>
       </c>
       <c r="E13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" t="s">
         <v>208</v>
-      </c>
-      <c r="F13" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4803,19 +4800,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
       </c>
       <c r="E14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" t="s">
         <v>103</v>
-      </c>
-      <c r="F14" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4823,19 +4820,19 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C15" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
       </c>
       <c r="E15" t="s">
+        <v>191</v>
+      </c>
+      <c r="F15" t="s">
         <v>192</v>
-      </c>
-      <c r="F15" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4843,19 +4840,19 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D16" t="s">
         <v>46</v>
       </c>
       <c r="E16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" t="s">
         <v>196</v>
-      </c>
-      <c r="F16" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4863,19 +4860,19 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C17" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D17" t="s">
         <v>46</v>
       </c>
       <c r="E17" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" t="s">
         <v>111</v>
-      </c>
-      <c r="F17" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4883,19 +4880,19 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C18" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D18" t="s">
         <v>46</v>
       </c>
       <c r="E18" t="s">
+        <v>199</v>
+      </c>
+      <c r="F18" t="s">
         <v>200</v>
-      </c>
-      <c r="F18" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4903,19 +4900,19 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
       </c>
       <c r="E19" t="s">
+        <v>203</v>
+      </c>
+      <c r="F19" t="s">
         <v>204</v>
-      </c>
-      <c r="F19" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4923,19 +4920,19 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
+        <v>357</v>
+      </c>
+      <c r="C20" t="s">
         <v>358</v>
       </c>
-      <c r="C20" t="s">
-        <v>359</v>
-      </c>
       <c r="D20" t="s">
         <v>46</v>
       </c>
       <c r="E20" t="s">
+        <v>274</v>
+      </c>
+      <c r="F20" t="s">
         <v>275</v>
-      </c>
-      <c r="F20" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4943,19 +4940,19 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C21" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D21" t="s">
         <v>46</v>
       </c>
       <c r="E21" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" t="s">
         <v>159</v>
-      </c>
-      <c r="F21" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4963,19 +4960,19 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D22" t="s">
         <v>46</v>
       </c>
       <c r="E22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s">
         <v>107</v>
-      </c>
-      <c r="F22" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4983,19 +4980,19 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D23" t="s">
         <v>46</v>
       </c>
       <c r="E23" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" t="s">
         <v>224</v>
-      </c>
-      <c r="F23" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -5003,19 +5000,19 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C24" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D24" t="s">
         <v>46</v>
       </c>
       <c r="E24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" t="s">
         <v>145</v>
-      </c>
-      <c r="F24" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -5023,19 +5020,19 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C25" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D25" t="s">
         <v>46</v>
       </c>
       <c r="E25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" t="s">
         <v>125</v>
-      </c>
-      <c r="F25" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -5043,19 +5040,19 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C26" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D26" t="s">
         <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -5063,19 +5060,19 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D27" t="s">
         <v>46</v>
       </c>
       <c r="E27" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" t="s">
         <v>90</v>
-      </c>
-      <c r="F27" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -5083,16 +5080,16 @@
         <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D28" t="s">
         <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F28" t="s">
         <v>48</v>
@@ -5103,16 +5100,16 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C29" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D29" t="s">
         <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s">
         <v>48</v>
@@ -5123,10 +5120,10 @@
         <v>101</v>
       </c>
       <c r="B30" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" t="s">
         <v>369</v>
-      </c>
-      <c r="C30" t="s">
-        <v>370</v>
       </c>
       <c r="D30" t="s">
         <v>46</v>
@@ -5143,10 +5140,10 @@
         <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C31" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D31" t="s">
         <v>46</v>
@@ -5155,7 +5152,7 @@
         <v>52</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -5163,19 +5160,19 @@
         <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C32" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D32" t="s">
         <v>46</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -5183,19 +5180,19 @@
         <v>71</v>
       </c>
       <c r="B33" t="s">
+        <v>372</v>
+      </c>
+      <c r="C33" t="s">
         <v>373</v>
       </c>
-      <c r="C33" t="s">
-        <v>374</v>
-      </c>
       <c r="D33" t="s">
         <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -5203,19 +5200,19 @@
         <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D34" t="s">
         <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -5223,19 +5220,19 @@
         <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C35" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D35" t="s">
         <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -5243,19 +5240,19 @@
         <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -5263,19 +5260,19 @@
         <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C37" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D37" t="s">
         <v>46</v>
       </c>
       <c r="E37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -5283,19 +5280,19 @@
         <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C38" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -5303,19 +5300,19 @@
         <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C39" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D39" t="s">
         <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -5323,19 +5320,19 @@
         <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C40" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D40" t="s">
         <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -5343,19 +5340,19 @@
         <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D41" t="s">
         <v>46</v>
       </c>
       <c r="E41" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -5363,19 +5360,19 @@
         <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D42" t="s">
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -5383,19 +5380,19 @@
         <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C43" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D43" t="s">
         <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -5403,19 +5400,19 @@
         <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D44" t="s">
         <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F44" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -5423,19 +5420,19 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C45" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D45" t="s">
         <v>46</v>
       </c>
       <c r="E45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F45" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -5443,19 +5440,19 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C46" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D46" t="s">
         <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F46" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -5463,19 +5460,19 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C47" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D47" t="s">
         <v>46</v>
       </c>
       <c r="E47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -5483,19 +5480,19 @@
         <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C48" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D48" t="s">
         <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -5503,19 +5500,19 @@
         <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C49" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D49" t="s">
         <v>46</v>
       </c>
       <c r="E49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -5523,19 +5520,19 @@
         <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C50" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D50" t="s">
         <v>46</v>
       </c>
       <c r="E50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -5543,19 +5540,19 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C51" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D51" t="s">
         <v>46</v>
       </c>
       <c r="E51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -5563,19 +5560,19 @@
         <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C52" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D52" t="s">
         <v>46</v>
       </c>
       <c r="E52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -5583,19 +5580,19 @@
         <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C53" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D53" t="s">
         <v>46</v>
       </c>
       <c r="E53" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F53" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -5603,19 +5600,19 @@
         <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C54" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D54" t="s">
         <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -5623,19 +5620,19 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C55" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D55" t="s">
         <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F55" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -5651,13 +5648,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" t="s">
         <v>397</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>398</v>
-      </c>
-      <c r="C1" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>
